--- a/results/monthly_investor_report_2026-08-27.xlsx
+++ b/results/monthly_investor_report_2026-08-27.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-28 13:27</t>
+          <t>Son Güncelleme: 2026-08-29 08:21</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -969,25 +969,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1301946401295221</v>
+        <v>0.1301946563809981</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>13019.46401295221</v>
+        <v>13019.46563809981</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.1079079459374078</v>
+        <v>0.1079080026692217</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1404.903618843673</v>
+        <v>1404.904532827915</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>237.313878638726</v>
+        <v>237.3138907906804</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>203.4899971008301</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>2.158158918748152</v>
+        <v>2.158160053384431</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1159312918589553</v>
+        <v>0.1159312909309919</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>11593.12918589553</v>
+        <v>11593.12909309919</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.0493707647628267</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>572.361653901909</v>
+        <v>572.3616493204826</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>399.5479186834463</v>
@@ -1053,25 +1053,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.08903847142738525</v>
+        <v>0.08903846940928832</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>8903.847142738525</v>
+        <v>8903.846940928832</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0768721535112086</v>
+        <v>0.07687214851712661</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>684.457904396932</v>
+        <v>684.4578444168445</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>434.7871319801505</v>
+        <v>434.7871299637899</v>
       </c>
       <c r="I22" s="8" t="n">
         <v>377.4784125939908</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.181395379749729</v>
+        <v>1.181395302999109</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.0854623464075606</v>
+        <v>0.08546234572348362</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>8546.23464075606</v>
+        <v>8546.234572348361</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0331174361060366</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>283.0293796624355</v>
+        <v>283.0293773969479</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>137.4046190021029</v>
@@ -1135,25 +1135,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.07937325017657668</v>
+        <v>0.07937323755523804</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>7937.325017657668</v>
+        <v>7937.323755523804</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0345253730965184</v>
+        <v>0.0345253100982498</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>274.0391076229605</v>
+        <v>274.038564009664</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>39.93267782296517</v>
+        <v>39.9326753912321</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>36.34287963504224</v>
+        <v>36.34288187878566</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.5904338423704588</v>
+        <v>0.5904333519434122</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>50000.00000000001</v>
+        <v>50000</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-28 13:27</t>
+          <t>Son Güncelleme: 2026-08-29 08:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1449,22 +1449,22 @@
         <v>380.75</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>0.0028744012948362</v>
+        <v>0.0028744014962105</v>
       </c>
       <c r="F8" s="16" t="n">
         <v>0.0493707647628267</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.2198951866897833</v>
+        <v>0.2198952770741356</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>381.8444282930089</v>
+        <v>381.8444283696822</v>
       </c>
       <c r="I8" s="15" t="n">
         <v>399.5479186834463</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>464.475092332135</v>
+        <v>464.4751267459771</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>359.396749902489</v>
@@ -1506,19 +1506,19 @@
         <v>214.1999969482422</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>0.0371203067330339</v>
+        <v>0.0371204201966619</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>0.1079079459374078</v>
+        <v>0.1079080026692217</v>
       </c>
       <c r="G9" s="16" t="n">
         <v>0.1786955851417817</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>222.1511665371759</v>
+        <v>222.1511908410847</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>237.313878638726</v>
+        <v>237.3138907906804</v>
       </c>
       <c r="J9" s="15" t="n">
         <v>252.4765907402762</v>
@@ -1569,7 +1569,7 @@
         <v>0.0331174361060366</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.1446542046234986</v>
+        <v>0.1446539767324788</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>131.8975631497201</v>
@@ -1578,7 +1578,7 @@
         <v>137.4046190021029</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>152.2390092149253</v>
+        <v>152.2389789054197</v>
       </c>
       <c r="K10" s="15" t="n">
         <v>126.35</v>
@@ -1620,25 +1620,25 @@
         <v>72.84999847412109</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.1195457879117688</v>
+        <v>-0.1195456773982677</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>-0.0366895635349088</v>
+        <v>-0.0366894684105838</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.05159344410234</v>
+        <v>0.0515933324042807</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>64.14108800716113</v>
+        <v>64.14109605806952</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>70.17716382658682</v>
+        <v>70.17717075639375</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>76.60858079825121</v>
+        <v>76.60857266104777</v>
       </c>
       <c r="K11" s="18" t="n">
-        <v>64.14108800716113</v>
+        <v>64.14109605806952</v>
       </c>
       <c r="L11" s="17" t="inlineStr">
         <is>
@@ -1677,25 +1677,25 @@
         <v>93.75</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.07730044685463951</v>
+        <v>-0.0773005255414696</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>0.0255523087465968</v>
+        <v>0.0255522639279874</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>0.0887438433689242</v>
+        <v>0.08874378886366099</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>86.50308310737755</v>
+        <v>86.50307573048723</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>96.14552894499344</v>
+        <v>96.14552474324883</v>
       </c>
       <c r="J12" s="21" t="n">
-        <v>102.0697353158367</v>
+        <v>102.0697302059682</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>86.50308310737755</v>
+        <v>86.50307573048723</v>
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
@@ -1737,19 +1737,19 @@
         <v>-0.0079710144927536</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>0.0768721535112086</v>
+        <v>0.07687214851712661</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>0.1767024655720609</v>
+        <v>0.1767023253641666</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>400.5317028985507</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>434.7871319801505</v>
+        <v>434.7871299637899</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>475.0936204747196</v>
+        <v>475.0935638657823</v>
       </c>
       <c r="K13" s="15" t="n">
         <v>377.4784125939908</v>
@@ -1791,25 +1791,25 @@
         <v>38.59999847412109</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>-0.0584745836348182</v>
+        <v>-0.0584745255067481</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0.0345253730965184</v>
+        <v>0.0345253100982498</v>
       </c>
       <c r="G14" s="16" t="n">
         <v>0.1107634622150022</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>36.34287963504224</v>
+        <v>36.34288187878566</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>39.93267782296517</v>
+        <v>39.9326753912321</v>
       </c>
       <c r="J14" s="15" t="n">
         <v>42.87546794660855</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>36.34287963504224</v>
+        <v>36.34288187878566</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
@@ -1848,22 +1848,22 @@
         <v>413.75</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>-0.0243525901521948</v>
+        <v>-0.0243524546491471</v>
       </c>
       <c r="F15" s="22" t="n">
         <v>0.0060687804495014</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>0.06314855114378599</v>
+        <v>0.0631485677683334</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>403.6741158245294</v>
+        <v>403.6741718889153</v>
       </c>
       <c r="I15" s="21" t="n">
         <v>416.2609579109812</v>
       </c>
       <c r="J15" s="21" t="n">
-        <v>439.8777130357414</v>
+        <v>439.877719914148</v>
       </c>
       <c r="K15" s="21" t="n">
         <v>393.0625</v>
@@ -1908,7 +1908,7 @@
         <v>-0.104751646118041</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-0.0315931209320554</v>
+        <v>-0.0315930645677514</v>
       </c>
       <c r="G16" s="19" t="n">
         <v>0.1136891323573432</v>
@@ -1917,7 +1917,7 @@
         <v>32.99885487050524</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>35.69547815351309</v>
+        <v>35.69548023110137</v>
       </c>
       <c r="J16" s="18" t="n">
         <v>41.05058209843357</v>
@@ -1965,19 +1965,19 @@
         <v>-0.0476951848926354</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>0.0046669165044877</v>
+        <v>0.0046668155230729</v>
       </c>
       <c r="G17" s="22" t="n">
-        <v>0.0596783413325591</v>
+        <v>0.0596784074389585</v>
       </c>
       <c r="H17" s="21" t="n">
         <v>97.89693789924074</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>103.2797620826614</v>
+        <v>103.2797517017717</v>
       </c>
       <c r="J17" s="21" t="n">
-        <v>108.9349367228687</v>
+        <v>108.9349435186068</v>
       </c>
       <c r="K17" s="21" t="n">
         <v>97.66000289916991</v>
@@ -2019,25 +2019,25 @@
         <v>273.5</v>
       </c>
       <c r="E18" s="25" t="n">
-        <v>-0.1062914431538463</v>
+        <v>-0.1062913807230041</v>
       </c>
       <c r="F18" s="25" t="n">
         <v>-0.0245398668646306</v>
       </c>
       <c r="G18" s="25" t="n">
-        <v>0.0358585890694043</v>
+        <v>0.0358586773669118</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>244.429290297423</v>
+        <v>244.4293073722584</v>
       </c>
       <c r="I18" s="24" t="n">
         <v>266.7883464125235</v>
       </c>
       <c r="J18" s="24" t="n">
-        <v>283.3073241104821</v>
+        <v>283.3073482598504</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>244.429290297423</v>
+        <v>244.4293073722584</v>
       </c>
       <c r="L18" s="23" t="inlineStr">
         <is>
@@ -2076,22 +2076,22 @@
         <v>151.5</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>-0.0355162004498606</v>
+        <v>-0.035516201414184</v>
       </c>
       <c r="F19" s="25" t="n">
-        <v>-0.0011988764109042</v>
+        <v>-0.0011987972727639</v>
       </c>
       <c r="G19" s="25" t="n">
-        <v>0.0637569974381122</v>
+        <v>0.0637570370071823</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>146.1192956318461</v>
+        <v>146.1192954857511</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>151.318370223748</v>
+        <v>151.3183822131762</v>
       </c>
       <c r="J19" s="24" t="n">
-        <v>161.159185111874</v>
+        <v>161.1591911065881</v>
       </c>
       <c r="K19" s="24" t="n">
         <v>143.925</v>
@@ -2163,7 +2163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-28 13:27</t>
+          <t>Son Güncelleme: 2026-08-29 08:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="J5" s="16" t="n">
-        <v>0.0200890131090384</v>
+        <v>0.0200890131090385</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>0.1079079459374078</v>
+        <v>0.1079080026692217</v>
       </c>
     </row>
     <row r="6">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.0189344060033612</v>
+        <v>0.018934406003361</v>
       </c>
       <c r="K6" s="16" t="n">
         <v>0.0331174361060366</v>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="J7" s="19" t="n">
-        <v>0.0252030048204396</v>
+        <v>0.0252030048204395</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>-0.0366895635349088</v>
+        <v>-0.0366894684105838</v>
       </c>
     </row>
     <row r="8">
@@ -2446,7 +2446,7 @@
         <v>0.0188918567133183</v>
       </c>
       <c r="K8" s="22" t="n">
-        <v>0.0255523087465968</v>
+        <v>0.0255522639279874</v>
       </c>
     </row>
     <row r="9">
@@ -2489,7 +2489,7 @@
         <v>0.0325344735678133</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>0.0768721535112086</v>
+        <v>0.07687214851712661</v>
       </c>
     </row>
     <row r="10">
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="J10" s="16" t="n">
-        <v>0.0224073510671082</v>
+        <v>0.0224073510671083</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>0.0345253730965184</v>
+        <v>0.0345253100982498</v>
       </c>
     </row>
     <row r="11">
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="J11" s="22" t="n">
-        <v>0.0191946226833422</v>
+        <v>0.0191946226833423</v>
       </c>
       <c r="K11" s="22" t="n">
         <v>0.0060687804495014</v>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="J12" s="19" t="n">
-        <v>0.0268491707380297</v>
+        <v>0.0268491707380296</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>-0.0315931209320554</v>
+        <v>-0.0315930645677514</v>
       </c>
     </row>
     <row r="13">
@@ -2661,7 +2661,7 @@
         <v>0.0200829643840794</v>
       </c>
       <c r="K13" s="22" t="n">
-        <v>0.0046669165044877</v>
+        <v>0.0046668155230729</v>
       </c>
     </row>
     <row r="14">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="J16" s="25" t="n">
-        <v>0.0221671481200846</v>
+        <v>0.0221671481200847</v>
       </c>
       <c r="K16" s="25" t="n">
         <v>-0.0245398668646306</v>
@@ -2833,7 +2833,7 @@
         <v>0.0196257181094786</v>
       </c>
       <c r="K17" s="27" t="n">
-        <v>0.0258272542822017</v>
+        <v>0.0258271723736069</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="J18" s="27" t="n">
-        <v>0.0165613004791113</v>
+        <v>0.0165613004791115</v>
       </c>
       <c r="K18" s="27" t="n">
-        <v>0.0283621099664455</v>
+        <v>0.0283622708857007</v>
       </c>
     </row>
     <row r="19">
@@ -2919,7 +2919,7 @@
         <v>0.0174669176767137</v>
       </c>
       <c r="K19" s="25" t="n">
-        <v>-0.0011988764109042</v>
+        <v>-0.0011987972727639</v>
       </c>
     </row>
     <row r="20">
@@ -2962,7 +2962,7 @@
         <v>0.0130331319051929</v>
       </c>
       <c r="K20" s="27" t="n">
-        <v>0.0294396733991557</v>
+        <v>0.0294396328657622</v>
       </c>
     </row>
   </sheetData>
@@ -2995,7 +2995,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-28 13:27</t>
+          <t>Son Güncelleme: 2026-08-29 08:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3114,7 +3114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-28 13:27</t>
+          <t>Son Güncelleme: 2026-08-29 08:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3365,7 +3365,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-28 13:27</t>
+          <t>Son Güncelleme: 2026-08-29 08:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3490,7 +3490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-28 13:27</t>
+          <t>Son Güncelleme: 2026-08-29 08:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3567,7 +3567,7 @@
         <v>7494.465345736011</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>11292893.23744916</v>
+        <v>11323067.84361813</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3597,7 +3597,7 @@
         <v>253751.8814931558</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>11292893.23744916</v>
+        <v>11323067.84361813</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3627,7 +3627,7 @@
         <v>855094.6352132326</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>11292893.23744916</v>
+        <v>11323067.84361813</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3657,7 +3657,7 @@
         <v>2352.37642182142</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>11292893.23744916</v>
+        <v>11323067.84361813</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3687,7 +3687,7 @@
         <v>-119.5771095832897</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>11292893.23744916</v>
+        <v>11323067.84361813</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3717,7 +3717,7 @@
         <v>-20731.00951479189</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>11292893.23744916</v>
+        <v>11323067.84361813</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.0635945709281962</v>

--- a/results/monthly_investor_report_2026-08-27.xlsx
+++ b/results/monthly_investor_report_2026-08-27.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-29 08:21</t>
+          <t>Son Güncelleme: 2026-08-30 07:35</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1301946563809981</v>
+        <v>0.1301946563809982</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>13019.46563809981</v>
+        <v>13019.46563809982</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.1079080026692217</v>
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.07937323755523804</v>
+        <v>0.07937323755523805</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>7937.323755523804</v>
+        <v>7937.323755523805</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0.0345253100982498</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>274.038564009664</v>
+        <v>274.0385640096641</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>39.9326753912321</v>
+        <v>39.93267539123209</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>36.34288187878566</v>
+        <v>36.34288187878565</v>
       </c>
       <c r="J24" s="6" t="n">
         <v>0.5904333519434122</v>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-29 08:21</t>
+          <t>Son Güncelleme: 2026-08-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1620,7 +1620,7 @@
         <v>72.84999847412109</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.1195456773982677</v>
+        <v>-0.1195456773982676</v>
       </c>
       <c r="F11" s="19" t="n">
         <v>-0.0366894684105838</v>
@@ -1677,25 +1677,25 @@
         <v>93.75</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.0773005255414696</v>
+        <v>-0.07730052554146941</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>0.0255522639279874</v>
+        <v>0.0255522639279876</v>
       </c>
       <c r="G12" s="22" t="n">
         <v>0.08874378886366099</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>86.50307573048723</v>
+        <v>86.50307573048724</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>96.14552474324883</v>
+        <v>96.14552474324884</v>
       </c>
       <c r="J12" s="21" t="n">
         <v>102.0697302059682</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>86.50307573048723</v>
+        <v>86.50307573048724</v>
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>0.07687214851712661</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>0.1767023253641666</v>
+        <v>0.1767023253641665</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>400.5317028985507</v>
@@ -1749,7 +1749,7 @@
         <v>434.7871299637899</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>475.0935638657823</v>
+        <v>475.0935638657822</v>
       </c>
       <c r="K13" s="15" t="n">
         <v>377.4784125939908</v>
@@ -1800,16 +1800,16 @@
         <v>0.1107634622150022</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>36.34288187878566</v>
+        <v>36.34288187878565</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>39.9326753912321</v>
+        <v>39.93267539123209</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>42.87546794660855</v>
+        <v>42.87546794660854</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>36.34288187878566</v>
+        <v>36.34288187878565</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>0.0060687804495014</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>0.0631485677683334</v>
+        <v>0.0631485677683335</v>
       </c>
       <c r="H15" s="21" t="n">
         <v>403.6741718889153</v>
@@ -1908,7 +1908,7 @@
         <v>-0.104751646118041</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-0.0315930645677514</v>
+        <v>-0.0315930645677513</v>
       </c>
       <c r="G16" s="19" t="n">
         <v>0.1136891323573432</v>
@@ -1965,13 +1965,13 @@
         <v>-0.0476951848926354</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>0.0046668155230729</v>
+        <v>0.0046668155230728</v>
       </c>
       <c r="G17" s="22" t="n">
         <v>0.0596784074389585</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>97.89693789924074</v>
+        <v>97.89693789924073</v>
       </c>
       <c r="I17" s="21" t="n">
         <v>103.2797517017717</v>
@@ -2019,7 +2019,7 @@
         <v>273.5</v>
       </c>
       <c r="E18" s="25" t="n">
-        <v>-0.1062913807230041</v>
+        <v>-0.1062913807230039</v>
       </c>
       <c r="F18" s="25" t="n">
         <v>-0.0245398668646306</v>
@@ -2163,7 +2163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-29 08:21</t>
+          <t>Son Güncelleme: 2026-08-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="E5" s="16" t="n">
-        <v>0.1064049080334841</v>
+        <v>0.1064049080334843</v>
       </c>
       <c r="F5" s="16" t="n">
         <v>0.1327339504737326</v>
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="J5" s="16" t="n">
-        <v>0.0200890131090385</v>
+        <v>0.0200890131090384</v>
       </c>
       <c r="K5" s="16" t="n">
         <v>0.1079080026692217</v>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.018934406003361</v>
+        <v>0.0189344060033611</v>
       </c>
       <c r="K6" s="16" t="n">
         <v>0.0331174361060366</v>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="J7" s="19" t="n">
-        <v>0.0252030048204395</v>
+        <v>0.0252030048204396</v>
       </c>
       <c r="K7" s="19" t="n">
         <v>-0.0366894684105838</v>
@@ -2446,7 +2446,7 @@
         <v>0.0188918567133183</v>
       </c>
       <c r="K8" s="22" t="n">
-        <v>0.0255522639279874</v>
+        <v>0.0255522639279876</v>
       </c>
     </row>
     <row r="9">
@@ -2512,13 +2512,13 @@
         </is>
       </c>
       <c r="E10" s="16" t="n">
-        <v>-0.1056534149539492</v>
+        <v>-0.1056534149539493</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>-0.0014077733762175</v>
+        <v>-0.0014077733762177</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.2468082657762476</v>
+        <v>0.2468082657762471</v>
       </c>
       <c r="H10" s="16" t="n">
         <v>0.1982309170737504</v>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="J10" s="16" t="n">
-        <v>0.0224073510671083</v>
+        <v>0.0224073510671082</v>
       </c>
       <c r="K10" s="16" t="n">
         <v>0.0345253100982498</v>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="J11" s="22" t="n">
-        <v>0.0191946226833423</v>
+        <v>0.0191946226833422</v>
       </c>
       <c r="K11" s="22" t="n">
         <v>0.0060687804495014</v>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="J12" s="19" t="n">
-        <v>0.0268491707380296</v>
+        <v>0.0268491707380297</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>-0.0315930645677514</v>
+        <v>-0.0315930645677513</v>
       </c>
     </row>
     <row r="13">
@@ -2641,13 +2641,13 @@
         </is>
       </c>
       <c r="E13" s="22" t="n">
-        <v>0.0138067209547487</v>
+        <v>0.0138067209547485</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>0.0178218123936417</v>
+        <v>0.0178218123936415</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>-0.1504131979193569</v>
+        <v>-0.150413197919357</v>
       </c>
       <c r="H13" s="22" t="n">
         <v>0.1254756146184883</v>
@@ -2661,7 +2661,7 @@
         <v>0.0200829643840794</v>
       </c>
       <c r="K13" s="22" t="n">
-        <v>0.0046668155230729</v>
+        <v>0.0046668155230728</v>
       </c>
     </row>
     <row r="14">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="J15" s="27" t="n">
-        <v>0.0184939262170705</v>
+        <v>0.0184939262170706</v>
       </c>
       <c r="K15" s="27" t="n">
         <v>0.0048076735037425</v>
@@ -2833,7 +2833,7 @@
         <v>0.0196257181094786</v>
       </c>
       <c r="K17" s="27" t="n">
-        <v>0.0258271723736069</v>
+        <v>0.0258271723736072</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="J18" s="27" t="n">
-        <v>0.0165613004791115</v>
+        <v>0.0165613004791113</v>
       </c>
       <c r="K18" s="27" t="n">
-        <v>0.0283622708857007</v>
+        <v>0.0283622708857009</v>
       </c>
     </row>
     <row r="19">
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="E20" s="27" t="n">
-        <v>-0.044738196178383</v>
+        <v>-0.0447381961783829</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>-0.09402121781031809</v>
+        <v>-0.094021217810318</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>-0.2091751301781463</v>
+        <v>-0.2091751301781461</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>-0.1050783758981807</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.0130331319051929</v>
+        <v>0.013033131905193</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>0.0294396328657622</v>
@@ -2995,7 +2995,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-29 08:21</t>
+          <t>Son Güncelleme: 2026-08-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3114,7 +3114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-29 08:21</t>
+          <t>Son Güncelleme: 2026-08-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3365,7 +3365,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-29 08:21</t>
+          <t>Son Güncelleme: 2026-08-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14575.5</v>
+        <v>14641.599609375</v>
       </c>
     </row>
     <row r="5">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13240.16153320312</v>
+        <v>13258.74703125</v>
       </c>
     </row>
     <row r="6">
@@ -3469,7 +3469,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3490,7 +3490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-29 08:21</t>
+          <t>Son Güncelleme: 2026-08-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3567,7 +3567,7 @@
         <v>7494.465345736011</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>11323067.84361813</v>
+        <v>11353242.4497871</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3597,7 +3597,7 @@
         <v>253751.8814931558</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>11323067.84361813</v>
+        <v>11353242.4497871</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3627,7 +3627,7 @@
         <v>855094.6352132326</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>11323067.84361813</v>
+        <v>11353242.4497871</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3657,7 +3657,7 @@
         <v>2352.37642182142</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>11323067.84361813</v>
+        <v>11353242.4497871</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3681,13 +3681,13 @@
         <v>38.59999847412109</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>-0.002068299649004457</v>
+        <v>-0.002068299649004679</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>-119.5771095832897</v>
+        <v>-119.5771095833043</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>11323067.84361813</v>
+        <v>11353242.4497871</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3711,13 +3711,13 @@
         <v>102.8000030517578</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>-0.006763255538571822</v>
+        <v>-0.006763255538572044</v>
       </c>
       <c r="F9" s="28" t="n">
         <v>-20731.00951479189</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>11323067.84361813</v>
+        <v>11353242.4497871</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.0635945709281962</v>

--- a/results/monthly_investor_report_2026-08-27.xlsx
+++ b/results/monthly_investor_report_2026-08-27.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-30 07:35</t>
+          <t>Son Güncelleme: 2026-08-31 07:46</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-30 07:35</t>
+          <t>Son Güncelleme: 2026-08-31 07:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2163,7 +2163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-30 07:35</t>
+          <t>Son Güncelleme: 2026-08-31 07:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2995,7 +2995,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-30 07:35</t>
+          <t>Son Güncelleme: 2026-08-31 07:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3114,7 +3114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-30 07:35</t>
+          <t>Son Güncelleme: 2026-08-31 07:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3365,7 +3365,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-30 07:35</t>
+          <t>Son Güncelleme: 2026-08-31 07:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3469,7 +3469,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3490,7 +3490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-30 07:35</t>
+          <t>Son Güncelleme: 2026-08-31 07:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3567,7 +3567,7 @@
         <v>7494.465345736011</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>11353242.4497871</v>
+        <v>11383417.05595607</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3597,7 +3597,7 @@
         <v>253751.8814931558</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>11353242.4497871</v>
+        <v>11383417.05595607</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3627,7 +3627,7 @@
         <v>855094.6352132326</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>11353242.4497871</v>
+        <v>11383417.05595607</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3657,7 +3657,7 @@
         <v>2352.37642182142</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>11353242.4497871</v>
+        <v>11383417.05595607</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3687,7 +3687,7 @@
         <v>-119.5771095833043</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>11353242.4497871</v>
+        <v>11383417.05595607</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3717,7 +3717,7 @@
         <v>-20731.00951479189</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>11353242.4497871</v>
+        <v>11383417.05595607</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.0635945709281962</v>
